--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488045_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488045_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9086</v>
+        <v>11.5741</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8704</v>
+        <v>8.199</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0381</v>
+        <v>3.3751</v>
       </c>
       <c r="G2" t="n">
         <v>6.7972</v>
@@ -610,13 +610,13 @@
         <v>3.568</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1975</v>
+        <v>1.863</v>
       </c>
       <c r="T2" t="n">
-        <v>0.694</v>
+        <v>1.0225</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.8405</v>
       </c>
       <c r="V2" t="n">
         <v>0.337</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.249700000000001</v>
+        <v>7.444</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2269</v>
+        <v>3.8424</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0228</v>
+        <v>3.6016</v>
       </c>
       <c r="G3" t="n">
         <v>2.4862</v>
@@ -688,13 +688,13 @@
         <v>3.568</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9201</v>
+        <v>2.1144</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4979</v>
+        <v>1.1133</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4222</v>
+        <v>1.001</v>
       </c>
       <c r="V3" t="n">
         <v>0.2666</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1593</v>
+        <v>4.7497</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0234</v>
+        <v>2.6857</v>
       </c>
       <c r="F4" t="n">
-        <v>3.136</v>
+        <v>2.064</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4223</v>
+        <v>0.9734</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0472</v>
+        <v>1.4552</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3751</v>
+        <v>-0.4819</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8476</v>
+        <v>2.1441</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1288</v>
+        <v>1.036</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2812</v>
+        <v>1.1081</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5747</v>
+        <v>-1.1708</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.4193</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6563</v>
+        <v>-1.59</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9911</v>
+        <v>2.7751</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9733</v>
+        <v>2.7751</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3239</v>
+        <v>1.0012</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5866</v>
+        <v>0.5416</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7373</v>
+        <v>0.4596</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9918</v>
+        <v>3.297</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0121</v>
+        <v>1.1412</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9798</v>
+        <v>2.1558</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9734</v>
+        <v>1.7782</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4552</v>
+        <v>-0.1599</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4819</v>
+        <v>1.9381</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1441</v>
+        <v>3.2224</v>
       </c>
       <c r="K5" t="n">
-        <v>1.036</v>
+        <v>-0.0398</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1081</v>
+        <v>3.2622</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1708</v>
+        <v>-1.4442</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4193</v>
+        <v>-0.1201</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.59</v>
+        <v>-1.3241</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7751</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7751</v>
+        <v>3.1716</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2433</v>
+        <v>1.3206</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.132</v>
+        <v>0.8922</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3754</v>
+        <v>0.4284</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6639</v>
+        <v>3.0953</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4239</v>
+        <v>-0.0608</v>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>3.1561</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7782</v>
+        <v>2.0093</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1599</v>
+        <v>0.6279</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9381</v>
+        <v>1.3813</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2224</v>
+        <v>2.1048</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0398</v>
+        <v>0.2087</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2622</v>
+        <v>1.8961</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4442</v>
+        <v>-0.0955</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1201</v>
+        <v>0.4193</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3241</v>
+        <v>-0.5148</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1982</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1716</v>
+        <v>2.3787</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6875</v>
+        <v>1.0067</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1749</v>
+        <v>0.8077</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5127</v>
+        <v>0.199</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1257</v>
+        <v>2.368</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0284</v>
+        <v>2.1303</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0973</v>
+        <v>0.2377</v>
       </c>
       <c r="G7" t="n">
         <v>0.9447</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.156</v>
+        <v>0.0863</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1138</v>
+        <v>-0.0119</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0422</v>
+        <v>0.0982</v>
       </c>
       <c r="V7" t="n">
         <v>0.9405</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2645</v>
+        <v>1.8131</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4704</v>
+        <v>-1.014</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7349</v>
+        <v>2.8271</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0093</v>
+        <v>-1.4223</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6279</v>
+        <v>-1.0472</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3813</v>
+        <v>-0.3751</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1048</v>
+        <v>-0.8476</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2087</v>
+        <v>-1.1288</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8961</v>
+        <v>0.2812</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0955</v>
+        <v>-0.5747</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4193</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5148</v>
+        <v>-0.6563</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3787</v>
+        <v>2.9733</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8241000000000001</v>
+        <v>1.9777</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6019</v>
+        <v>1.5492</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2222</v>
+        <v>0.4284</v>
       </c>
       <c r="V8" t="n">
-        <v>0.674</v>
+        <v>0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2212</v>
+        <v>-0.4519</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9349</v>
+        <v>-1.0533</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7137</v>
+        <v>0.6014</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6102</v>
@@ -1234,13 +1234,13 @@
         <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4485</v>
+        <v>1.2178</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6829</v>
+        <v>0.5645</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.6533</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2666</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6755</v>
+        <v>-0.7036</v>
       </c>
       <c r="E11" t="n">
         <v>-0.9085</v>
       </c>
       <c r="F11" t="n">
-        <v>0.233</v>
+        <v>0.2049</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7192</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0437</v>
+        <v>0.0156</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2933</v>
+        <v>0.2652</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7404</v>
+        <v>-1.7685</v>
       </c>
       <c r="E12" t="n">
         <v>-1.9735</v>
       </c>
       <c r="F12" t="n">
-        <v>0.233</v>
+        <v>0.2049</v>
       </c>
       <c r="G12" t="n">
         <v>-0.793</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0437</v>
+        <v>0.0156</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2933</v>
+        <v>0.2652</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8297</v>
+        <v>-2.5843</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9629</v>
+        <v>-4.7176</v>
       </c>
       <c r="F13" t="n">
         <v>2.1333</v>
@@ -1468,10 +1468,10 @@
         <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0293</v>
+        <v>1.2747</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5616</v>
+        <v>0.6838</v>
       </c>
       <c r="U13" t="n">
         <v>0.5909</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.1994</v>
+        <v>29.1356</v>
       </c>
       <c r="E14" t="n">
-        <v>7.637600000000002</v>
+        <v>8.573600000000003</v>
       </c>
       <c r="F14" t="n">
         <v>20.5619</v>
@@ -1513,7 +1513,7 @@
         <v>9.3439</v>
       </c>
       <c r="H14" t="n">
-        <v>6.033600000000001</v>
+        <v>6.0336</v>
       </c>
       <c r="I14" t="n">
         <v>3.3101</v>
@@ -1525,7 +1525,7 @@
         <v>5.916</v>
       </c>
       <c r="L14" t="n">
-        <v>9.844799999999999</v>
+        <v>9.844800000000003</v>
       </c>
       <c r="M14" t="n">
         <v>-6.417</v>
@@ -1546,13 +1546,13 @@
         <v>21.8044</v>
       </c>
       <c r="S14" t="n">
-        <v>10.9574</v>
+        <v>11.8936</v>
       </c>
       <c r="T14" t="n">
-        <v>5.727799999999999</v>
+        <v>6.663699999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>5.229800000000001</v>
+        <v>5.229699999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.9515</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>A. CONTRERAS RUBIÑO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6802</v>
+        <v>0.6027</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2149</v>
+        <v>0.6027</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4653</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3956</v>
+        <v>0.6027</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0915</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4871</v>
+        <v>0.6027</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4341</v>
+        <v>0.6027</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9754</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4586</v>
+        <v>0.6027</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0385</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.067</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0285</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1296</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2458</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1162</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBIÑO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6027</v>
+        <v>0.5281</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6027</v>
+        <v>0.0112</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.5169</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6027</v>
+        <v>2.3956</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.0915</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6027</v>
+        <v>2.4871</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6027</v>
+        <v>3.4341</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.9754</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6027</v>
+        <v>2.4586</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.0385</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.067</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.0285</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.2817</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.4495</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.1678</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5313</v>
+        <v>0.0682</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6396</v>
+        <v>2.047</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1709</v>
+        <v>-1.9789</v>
       </c>
       <c r="G18" t="n">
         <v>0.371</v>
@@ -1858,13 +1858,13 @@
         <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.6863</v>
+        <v>-2.0869</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3727</v>
+        <v>-0.9653</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3136</v>
+        <v>-1.1216</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5997</v>
+        <v>-0.2556</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3404</v>
+        <v>-1.1367</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7407</v>
+        <v>0.8811</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6309</v>
@@ -1936,13 +1936,13 @@
         <v>0.7929</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5635</v>
+        <v>-0.2193</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.624</v>
+        <v>-0.4202</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0605</v>
+        <v>0.2009</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7206</v>
+        <v>-3.4033</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2348</v>
+        <v>-1.1329</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4858</v>
+        <v>-2.2703</v>
       </c>
       <c r="G20" t="n">
         <v>0.5948</v>
@@ -2014,13 +2014,13 @@
         <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3223</v>
+        <v>-1.0049</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6826</v>
+        <v>-0.5807</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6397</v>
+        <v>-0.4242</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0109</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2554</v>
+        <v>-3.8232</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9935</v>
+        <v>-2.377</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.262</v>
+        <v>-1.4462</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0628</v>
+        <v>1.1052</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1654</v>
+        <v>-1.2269</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8974</v>
+        <v>2.3321</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9416</v>
+        <v>3.8884</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1023</v>
+        <v>-0.5713</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1607</v>
+        <v>4.4597</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1212</v>
+        <v>-2.7832</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0631</v>
+        <v>-0.6556</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0581</v>
+        <v>-2.1276</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3964</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-4.9556</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7962</v>
+        <v>-1.4793</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0696</v>
+        <v>-0.6359</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7266</v>
+        <v>-0.8435</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>J. GIANNETTO DE LEON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.281</v>
+        <v>-3.9392</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4789</v>
+        <v>-4.3962</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8021</v>
+        <v>0.457</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1052</v>
+        <v>-1.8477</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2269</v>
+        <v>-0.7171</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3321</v>
+        <v>-1.1307</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8884</v>
+        <v>-1.9369</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5713</v>
+        <v>-0.659</v>
       </c>
       <c r="L22" t="n">
-        <v>4.4597</v>
+        <v>-1.2779</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7832</v>
+        <v>0.0891</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6556</v>
+        <v>-0.0581</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1276</v>
+        <v>0.1472</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7751</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.9556</v>
+        <v>-2.1805</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1805</v>
+        <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9371</v>
+        <v>-0.7039</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7377</v>
+        <v>-0.2789</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1994</v>
+        <v>-0.425</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. GIANNETTO DE LEON</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5432</v>
+        <v>-4.4116</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8037</v>
+        <v>-4.5381</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2605</v>
+        <v>0.1265</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8477</v>
+        <v>-2.7391</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7171</v>
+        <v>-2.1403</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1307</v>
+        <v>-0.5988</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9369</v>
+        <v>-1.3181</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.659</v>
+        <v>-1.217</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2779</v>
+        <v>-0.1011</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0891</v>
+        <v>-1.421</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0581</v>
+        <v>-0.9233</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1472</v>
+        <v>-0.4977</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.1805</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7929</v>
+        <v>2.7751</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3079</v>
+        <v>-2.0006</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6864</v>
+        <v>-1.0396</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.961</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1645</v>
+        <v>-4.6779</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0475</v>
+        <v>-3.2991</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1171</v>
+        <v>-1.3789</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.7391</v>
+        <v>-3.0628</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1403</v>
+        <v>-2.1654</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5988</v>
+        <v>-0.8974</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3181</v>
+        <v>-0.9416</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.217</v>
+        <v>-1.1023</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1011</v>
+        <v>0.1607</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.421</v>
+        <v>-2.1212</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9233</v>
+        <v>-1.0631</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4977</v>
+        <v>-1.0581</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1805</v>
+        <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7751</v>
+        <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.7535</v>
+        <v>-1.2187</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5489</v>
+        <v>-0.3752</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2046</v>
+        <v>-0.8435</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9892</v>
+        <v>-8.132</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.7229</v>
+        <v>-6.9454</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2663</v>
+        <v>-1.1866</v>
       </c>
       <c r="G25" t="n">
         <v>-6.7353</v>
@@ -2404,13 +2404,13 @@
         <v>2.3787</v>
       </c>
       <c r="S25" t="n">
-        <v>0.539</v>
+        <v>-0.6038</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7381</v>
+        <v>-0.4844</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1991</v>
+        <v>-0.1195</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-28.1993</v>
+        <v>-26.8411</v>
       </c>
       <c r="E26" t="n">
         <v>-20.5618</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.637699999999999</v>
+        <v>-6.279400000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-9.3438</v>
@@ -2455,13 +2455,13 @@
         <v>-3.3102</v>
       </c>
       <c r="J26" t="n">
-        <v>6.4171</v>
+        <v>6.417100000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1177999999999995</v>
+        <v>-0.1178000000000008</v>
       </c>
       <c r="L26" t="n">
-        <v>6.5347</v>
+        <v>6.534700000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-15.7609</v>
@@ -2470,7 +2470,7 @@
         <v>-5.915999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.844900000000001</v>
+        <v>-9.844899999999999</v>
       </c>
       <c r="P26" t="n">
         <v>-5.946600000000001</v>
@@ -2482,13 +2482,13 @@
         <v>15.8579</v>
       </c>
       <c r="S26" t="n">
-        <v>-10.9574</v>
+        <v>-9.5991</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.2296</v>
+        <v>-5.2297</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.7278</v>
+        <v>-4.3696</v>
       </c>
       <c r="V26" t="n">
         <v>-1.9515</v>
